--- a/Enter a test cases for Windows Notepad Application.xlsx
+++ b/Enter a test cases for Windows Notepad Application.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Pass / Fail / Not executed / Suspended</t>
   </si>
@@ -100,6 +100,102 @@
   </si>
   <si>
     <t>Test entire functionality of Windows Notepad Application.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that you see this application                                        </t>
+  </si>
+  <si>
+    <t>Search for the Notepad Application.</t>
+  </si>
+  <si>
+    <t>Click on the notepad application.</t>
+  </si>
+  <si>
+    <t>Verify that window application is open                                                                                                                                                                                                                                                                                                                                                                                                                                             .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that multile tab option you can see </t>
+  </si>
+  <si>
+    <t>Type you content on the blank tab.</t>
+  </si>
+  <si>
+    <t>Verify you are able to type on it.</t>
+  </si>
+  <si>
+    <t>Verify you are able to to see the save as option and dialog box to give name of file and save.</t>
+  </si>
+  <si>
+    <t>Click on File Menu.</t>
+  </si>
+  <si>
+    <t>Verify that you see this tab.</t>
+  </si>
+  <si>
+    <t>i. Click on Save as Option.            ii. Give the name of file on  dialog box.                                          iii. Then click on save.</t>
+  </si>
+  <si>
+    <t>i. Select the conent.                     ii. Click on Edit Menu.                     iii. Click on font option.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the Font section                         i.Click on Family.                           ii. Select the font family e.g. "Calibri".                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the Font section                         i.Click on Stye                            ii. Select the font Style e.g. "Bold Italic".                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the Font section                         i.Click on Size                             ii. Select the font Size e.g. "20".                                        </t>
+  </si>
+  <si>
+    <t>Verify that you see the font family changed.</t>
+  </si>
+  <si>
+    <t>Verify that you see the style of font changed.</t>
+  </si>
+  <si>
+    <t>Verify that you see the size of font increased.</t>
+  </si>
+  <si>
+    <t>Click Edit -&gt; Time/Date</t>
+  </si>
+  <si>
+    <t>Verify the current date and time displayed.</t>
+  </si>
+  <si>
+    <t>Click View -&gt; Zoom -&gt; Zoom In.</t>
+  </si>
+  <si>
+    <t>Click View -&gt; Zoom -&gt; Zoom Out.</t>
+  </si>
+  <si>
+    <t>Verify the page zoomed Out.</t>
+  </si>
+  <si>
+    <t>Verify the page zoomed In.</t>
+  </si>
+  <si>
+    <t>Click on Table Icon showing in the Top center.        -&gt; Insert -&gt; Define the rows an columns.</t>
+  </si>
+  <si>
+    <t>Verify that the table of given size are see.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on Link Icon showing in the Top Center.        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify this tab shows </t>
+  </si>
+  <si>
+    <t>Verify the Link shows with the name we given.</t>
+  </si>
+  <si>
+    <t>In the link dialog box Enter the name of link "GitHub" and url address i.e. link of github. Then click insert.</t>
+  </si>
+  <si>
+    <t>Click Setting -&gt; App Theme -&gt; Click on Dark Theme.</t>
+  </si>
+  <si>
+    <t>Verify the theme of notepad changed to dark.</t>
   </si>
 </sst>
 </file>
@@ -109,7 +205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,12 +221,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -474,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -498,26 +588,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -535,67 +622,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,6 +700,445 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28014</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161084</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>308161</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>441231</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="1267665" y="2990569"/>
+          <a:ext cx="280147" cy="280147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>399211</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>203106</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1120586" cy="913577"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2745443" y="3536856"/>
+          <a:ext cx="1120586" cy="913577"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>14007</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>182095</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>294154</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>462242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="2360239" y="3011580"/>
+          <a:ext cx="280147" cy="280147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>455691</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>178706</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1452623" cy="988875"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="9088" r="1942"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2790852" y="5048746"/>
+          <a:ext cx="1452623" cy="988875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>84045</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>518271</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>820011</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1722904</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2430277" y="6954650"/>
+          <a:ext cx="1765506" cy="1204633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>126065</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>182096</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>819430</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1323964</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2472297" y="8502464"/>
+          <a:ext cx="1722905" cy="1141868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>221621</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>174467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>377228</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>330074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect l="13813" t="23375" r="4517" b="5134"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1457042" y="12264616"/>
+          <a:ext cx="155607" cy="155607"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>213827</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>194388</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>394827</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>327757</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1457909" y="12887908"/>
+          <a:ext cx="181000" cy="133369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>194389</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>748392</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>890223</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2488163" y="12887909"/>
+          <a:ext cx="1642576" cy="695834"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48599</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>359618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>905532</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>777551</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400691" y="14005638"/>
+          <a:ext cx="1887188" cy="417933"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -895,99 +1421,99 @@
   <sheetData>
     <row r="1" spans="2:11" ht="1.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="44" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="14"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="10"/>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="28" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="27" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="10"/>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="28" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="10"/>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="42" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="38" t="s">
+      <c r="F4" s="38"/>
+      <c r="G4" s="37" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="28" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="36" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="36"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="33"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="30" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="28" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="11"/>
@@ -998,16 +1524,16 @@
       <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26">
+      <c r="F7" s="26"/>
+      <c r="G7" s="25">
         <v>1</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>5</v>
       </c>
       <c r="I7" s="11"/>
@@ -1018,16 +1544,16 @@
       <c r="B8" s="12">
         <v>2</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="26">
+      <c r="F8" s="26"/>
+      <c r="G8" s="25">
         <v>2</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="11"/>
@@ -1041,8 +1567,8 @@
       <c r="C9" s="9"/>
       <c r="D9" s="11"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="26">
+      <c r="F9" s="26"/>
+      <c r="G9" s="25">
         <v>3</v>
       </c>
       <c r="H9" s="9"/>
@@ -1057,8 +1583,8 @@
       <c r="C10" s="4"/>
       <c r="D10" s="6"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="24">
+      <c r="F10" s="24"/>
+      <c r="G10" s="23">
         <v>4</v>
       </c>
       <c r="H10" s="4"/>
@@ -1067,46 +1593,46 @@
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
@@ -1121,34 +1647,38 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15" t="s">
+      <c r="D15" s="15"/>
+      <c r="E15" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="15" t="s">
+      <c r="F15" s="15"/>
+      <c r="G15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="15" t="s">
+      <c r="H15" s="16"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K15" s="14"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="9"/>
+      <c r="C16" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="F16" s="10"/>
       <c r="G16" s="9"/>
       <c r="H16" s="11"/>
@@ -1156,13 +1686,17 @@
       <c r="J16" s="9"/>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>2</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="27" t="s">
+        <v>27</v>
+      </c>
       <c r="D17" s="10"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="27" t="s">
+        <v>28</v>
+      </c>
       <c r="F17" s="10"/>
       <c r="G17" s="9"/>
       <c r="H17" s="11"/>
@@ -1170,27 +1704,33 @@
       <c r="J17" s="9"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="12">
         <v>3</v>
       </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="27" t="s">
+        <v>30</v>
+      </c>
       <c r="D18" s="10"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="27" t="s">
+        <v>31</v>
+      </c>
       <c r="F18" s="10"/>
       <c r="G18" s="9"/>
       <c r="H18" s="11"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="12">
         <v>4</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="27" t="s">
+        <v>33</v>
+      </c>
       <c r="D19" s="10"/>
-      <c r="E19" s="9"/>
+      <c r="E19" s="27" t="s">
+        <v>29</v>
+      </c>
       <c r="F19" s="10"/>
       <c r="G19" s="9"/>
       <c r="H19" s="11"/>
@@ -1198,13 +1738,17 @@
       <c r="J19" s="9"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="12">
         <v>5</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="D20" s="10"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="27" t="s">
+        <v>32</v>
+      </c>
       <c r="F20" s="10"/>
       <c r="G20" s="9"/>
       <c r="H20" s="11"/>
@@ -1212,13 +1756,17 @@
       <c r="J20" s="9"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="12">
         <v>6</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="27" t="s">
+        <v>36</v>
+      </c>
       <c r="D21" s="10"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="27" t="s">
+        <v>34</v>
+      </c>
       <c r="F21" s="10"/>
       <c r="G21" s="9"/>
       <c r="H21" s="11"/>
@@ -1226,13 +1774,17 @@
       <c r="J21" s="9"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="12">
         <v>7</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="27" t="s">
+        <v>37</v>
+      </c>
       <c r="D22" s="10"/>
-      <c r="E22" s="9"/>
+      <c r="E22" s="27" t="s">
+        <v>40</v>
+      </c>
       <c r="F22" s="10"/>
       <c r="G22" s="9"/>
       <c r="H22" s="11"/>
@@ -1240,13 +1792,17 @@
       <c r="J22" s="9"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="12">
         <v>8</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="27" t="s">
+        <v>38</v>
+      </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="27" t="s">
+        <v>41</v>
+      </c>
       <c r="F23" s="10"/>
       <c r="G23" s="9"/>
       <c r="H23" s="11"/>
@@ -1254,13 +1810,17 @@
       <c r="J23" s="9"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12">
         <v>9</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="27" t="s">
+        <v>39</v>
+      </c>
       <c r="D24" s="10"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="27" t="s">
+        <v>42</v>
+      </c>
       <c r="F24" s="10"/>
       <c r="G24" s="9"/>
       <c r="H24" s="11"/>
@@ -1268,13 +1828,17 @@
       <c r="J24" s="9"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="12">
         <v>10</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="9"/>
+      <c r="E25" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="F25" s="10"/>
       <c r="G25" s="9"/>
       <c r="H25" s="11"/>
@@ -1282,13 +1846,17 @@
       <c r="J25" s="9"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="12">
         <v>11</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="D26" s="10"/>
-      <c r="E26" s="9"/>
+      <c r="E26" s="27" t="s">
+        <v>48</v>
+      </c>
       <c r="F26" s="10"/>
       <c r="G26" s="9"/>
       <c r="H26" s="11"/>
@@ -1296,13 +1864,17 @@
       <c r="J26" s="9"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="12">
         <v>12</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="D27" s="10"/>
-      <c r="E27" s="9"/>
+      <c r="E27" s="27" t="s">
+        <v>47</v>
+      </c>
       <c r="F27" s="10"/>
       <c r="G27" s="9"/>
       <c r="H27" s="11"/>
@@ -1310,13 +1882,17 @@
       <c r="J27" s="9"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="12">
         <v>13</v>
       </c>
-      <c r="C28" s="9"/>
+      <c r="C28" s="27" t="s">
+        <v>49</v>
+      </c>
       <c r="D28" s="10"/>
-      <c r="E28" s="9"/>
+      <c r="E28" s="27" t="s">
+        <v>50</v>
+      </c>
       <c r="F28" s="10"/>
       <c r="G28" s="9"/>
       <c r="H28" s="11"/>
@@ -1324,13 +1900,17 @@
       <c r="J28" s="9"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12">
         <v>14</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="27" t="s">
+        <v>51</v>
+      </c>
       <c r="D29" s="10"/>
-      <c r="E29" s="9"/>
+      <c r="E29" s="27" t="s">
+        <v>52</v>
+      </c>
       <c r="F29" s="10"/>
       <c r="G29" s="9"/>
       <c r="H29" s="11"/>
@@ -1338,13 +1918,17 @@
       <c r="J29" s="9"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12">
         <v>15</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="27" t="s">
+        <v>54</v>
+      </c>
       <c r="D30" s="10"/>
-      <c r="E30" s="9"/>
+      <c r="E30" s="27" t="s">
+        <v>53</v>
+      </c>
       <c r="F30" s="10"/>
       <c r="G30" s="9"/>
       <c r="H30" s="11"/>
@@ -1352,13 +1936,17 @@
       <c r="J30" s="9"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="12">
         <v>16</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="27" t="s">
+        <v>55</v>
+      </c>
       <c r="D31" s="10"/>
-      <c r="E31" s="9"/>
+      <c r="E31" s="27" t="s">
+        <v>56</v>
+      </c>
       <c r="F31" s="10"/>
       <c r="G31" s="9"/>
       <c r="H31" s="11"/>
@@ -1531,9 +2119,10 @@
       <c r="K44" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="103">
     <mergeCell ref="G34:I34"/>
     <mergeCell ref="J34:K34"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="G35:I35"/>
@@ -1599,9 +2188,7 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="C20:D20"/>
@@ -1638,5 +2225,7 @@
     <mergeCell ref="H8:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>